--- a/docs/Regional_Adaptation_Layer.xlsx
+++ b/docs/Regional_Adaptation_Layer.xlsx
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>De-identification effectively needed to avoid full PII obligations (consent-heavy regime). Threshold to be set with counsel.</t>
+          <t>De-identification effectively needed to avoid full PII obligations (consent-heavy regime). k = 5 like the baseline, kept as an adjustable number per jurisdiction in the policy file.</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
